--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pathways Quality EXCELLENCE " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pathways Quality STAR Leader" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pathways Quality EXCELLENCE " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pathways Quality STAR Leader" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5947,7 +5947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5955,8 +5955,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6015,11 +6014,6 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Qualifying Date</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
           <t>Ovation 2027</t>
         </is>
       </c>
@@ -6046,11 +6040,6 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6077,11 +6066,6 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6108,11 +6092,6 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6139,11 +6118,6 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6169,11 +6143,6 @@
         <v>3</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6201,11 +6170,6 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6232,11 +6196,6 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6263,11 +6222,6 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6294,11 +6248,6 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6325,11 +6274,6 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6356,11 +6300,6 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6387,11 +6326,6 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6418,11 +6352,6 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6449,11 +6378,6 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6480,11 +6404,6 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6511,11 +6430,6 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6542,11 +6456,6 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6573,11 +6482,6 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6604,11 +6508,6 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6635,11 +6534,6 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -6664,12 +6558,7 @@
       <c r="E27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -6691,12 +6580,7 @@
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -6718,12 +6602,7 @@
       <c r="E29" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -6745,12 +6624,7 @@
       <c r="E30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -6772,12 +6646,7 @@
       <c r="E31" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -6799,12 +6668,7 @@
       <c r="E32" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -6826,12 +6690,7 @@
       <c r="E33" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -6853,12 +6712,7 @@
       <c r="E34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -6880,12 +6734,7 @@
       <c r="E35" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -6907,12 +6756,7 @@
       <c r="E36" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -6934,12 +6778,7 @@
       <c r="E37" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -6961,12 +6800,7 @@
       <c r="E38" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -6988,12 +6822,7 @@
       <c r="E39" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -7015,12 +6844,7 @@
       <c r="E40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -7042,12 +6866,7 @@
       <c r="E41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -7069,12 +6888,7 @@
       <c r="E42" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -7096,17 +6910,12 @@
       <c r="E43" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>First 20 clubs (by qualifying date) recognized at Ovation 2027. All qualifying clubs recognized on District social media.</t>
+          <t>First 20 clubs (by qualifying date, not shown here) recognized at Ovation 2027. All qualifying clubs recognized on District social media.</t>
         </is>
       </c>
     </row>
@@ -7121,7 +6930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7129,8 +6938,6 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7187,12 +6994,6 @@
           <t>Level 3</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Qualifying Date</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -7214,12 +7015,6 @@
       <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -7241,12 +7036,6 @@
       <c r="E8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -7268,12 +7057,6 @@
       <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -7295,12 +7078,6 @@
       <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -7322,12 +7099,6 @@
       <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -7349,12 +7120,6 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -7376,12 +7141,6 @@
       <c r="E13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -7403,12 +7162,6 @@
       <c r="E14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -7430,12 +7183,6 @@
       <c r="E15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -7457,12 +7204,6 @@
       <c r="E16" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -7484,12 +7225,6 @@
       <c r="E17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -7511,12 +7246,6 @@
       <c r="E18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -7538,12 +7267,6 @@
       <c r="E19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -7565,12 +7288,6 @@
       <c r="E20" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -7592,12 +7309,6 @@
       <c r="E21" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -7619,12 +7330,6 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -7646,12 +7351,6 @@
       <c r="E23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -7673,12 +7372,6 @@
       <c r="E24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -7700,12 +7393,6 @@
       <c r="E25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -7727,12 +7414,6 @@
       <c r="E26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -7754,12 +7435,6 @@
       <c r="E27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -7781,12 +7456,6 @@
       <c r="E28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -7808,12 +7477,6 @@
       <c r="E29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -7835,12 +7498,6 @@
       <c r="E30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -7862,12 +7519,6 @@
       <c r="E31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -7889,12 +7540,6 @@
       <c r="E32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -7916,12 +7561,6 @@
       <c r="E33" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -7943,12 +7582,6 @@
       <c r="E34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -7970,12 +7603,6 @@
       <c r="E35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -7997,12 +7624,6 @@
       <c r="E36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -8024,12 +7645,6 @@
       <c r="E37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -8051,12 +7666,6 @@
       <c r="E38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -8078,12 +7687,6 @@
       <c r="E39" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -8105,12 +7708,6 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -8132,12 +7729,6 @@
       <c r="E41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -8159,12 +7750,6 @@
       <c r="E42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -8186,12 +7771,6 @@
       <c r="E43" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -8213,12 +7792,6 @@
       <c r="E44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -8240,12 +7813,6 @@
       <c r="E45" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -8267,12 +7834,6 @@
       <c r="E46" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -8294,12 +7855,6 @@
       <c r="E47" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -8321,12 +7876,6 @@
       <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -8348,12 +7897,6 @@
       <c r="E49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -8375,12 +7918,6 @@
       <c r="E50" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -8402,12 +7939,6 @@
       <c r="E51" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -8429,12 +7960,6 @@
       <c r="E52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -8456,12 +7981,6 @@
       <c r="E53" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -8483,12 +8002,6 @@
       <c r="E54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -10,8 +10,8 @@
     <sheet name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pathways Quality EXCELLENCE " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pathways Quality STAR Leader" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Clubs Qualifying — Pathways " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Clubs Qualifying — Pathway_2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>21</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>21</v>
@@ -1232,25 +1232,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>21</v>
@@ -1262,22 +1262,22 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2</v>
@@ -1292,22 +1292,22 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>2</v>
@@ -1322,25 +1322,25 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>19</v>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>19</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1394,13 +1394,13 @@
         <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>19</v>
@@ -1502,25 +1502,25 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>19</v>
@@ -1532,16 +1532,16 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>4</v>
@@ -1550,7 +1550,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>18</v>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -1577,10 +1577,10 @@
         <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>18</v>
@@ -1592,22 +1592,22 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="n">
         <v>3</v>
@@ -1622,22 +1622,22 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>3</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>18</v>
@@ -1682,22 +1682,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>2</v>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>18</v>
@@ -1742,25 +1742,25 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>18</v>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G32" s="8" t="n">
         <v>2</v>
@@ -1832,25 +1832,25 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>17</v>
@@ -1862,16 +1862,16 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>4</v>
@@ -1880,7 +1880,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>17</v>
@@ -1892,22 +1892,22 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>3</v>
@@ -1952,25 +1952,25 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>17</v>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>3</v>
@@ -2042,22 +2042,22 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>2</v>
@@ -2072,22 +2072,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2</v>
@@ -2102,25 +2102,25 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2132,16 +2132,16 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>4</v>
@@ -2150,7 +2150,7 @@
         <v>2</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>15</v>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -2192,16 +2192,16 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>15</v>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
@@ -2240,7 +2240,7 @@
         <v>3</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>15</v>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>15</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
@@ -2297,10 +2297,10 @@
         <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>15</v>
@@ -2312,25 +2312,25 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>15</v>
@@ -2342,16 +2342,16 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
@@ -2360,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>15</v>
@@ -2372,16 +2372,16 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>4</v>
@@ -2390,7 +2390,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>15</v>
@@ -2402,25 +2402,25 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>15</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -2441,16 +2441,16 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>14</v>
@@ -2462,22 +2462,22 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>2</v>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
@@ -2507,10 +2507,10 @@
         <v>4</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>14</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
@@ -2552,19 +2552,19 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>2</v>
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
@@ -2612,22 +2612,22 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8" t="n">
         <v>2</v>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>4</v>
@@ -2690,7 +2690,7 @@
         <v>2</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>13</v>
@@ -2702,22 +2702,22 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>2</v>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -2762,16 +2762,16 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>4</v>
@@ -2780,7 +2780,7 @@
         <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>13</v>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2807,10 +2807,10 @@
         <v>4</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>13</v>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
@@ -2837,10 +2837,10 @@
         <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>13</v>
@@ -2852,16 +2852,16 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>4</v>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>13</v>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2897,10 +2897,10 @@
         <v>4</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" s="6" t="n">
         <v>13</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -3002,22 +3002,22 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>2</v>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
@@ -3362,22 +3362,22 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
@@ -3422,25 +3422,25 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>11</v>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="8" t="n">
         <v>11</v>
@@ -3512,16 +3512,16 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="8" t="n">
         <v>2</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H90" s="8" t="n">
         <v>10</v>
@@ -3542,16 +3542,16 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>2</v>
@@ -3560,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>10</v>
@@ -3572,22 +3572,22 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>2</v>
@@ -3632,25 +3632,25 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="8" t="n">
         <v>10</v>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>8</v>
@@ -3782,25 +3782,25 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
         <v>8</v>
@@ -3842,22 +3842,22 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>1</v>
@@ -3932,12 +3932,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -3977,10 +3977,10 @@
         <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6" t="n">
         <v>7</v>
@@ -3992,25 +3992,25 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
         <v>7</v>
@@ -4022,25 +4022,25 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>6</v>
@@ -4052,25 +4052,25 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" s="8" t="n">
         <v>6</v>
@@ -4082,22 +4082,22 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
         <v>0</v>
@@ -4112,25 +4112,25 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="8" t="n">
         <v>6</v>
@@ -4142,25 +4142,25 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
         <v>6</v>
@@ -4172,25 +4172,25 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H112" s="8" t="n">
         <v>6</v>
@@ -4202,25 +4202,25 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>6</v>
@@ -4232,25 +4232,25 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114" s="8" t="n">
         <v>6</v>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6" t="n">
         <v>6</v>
@@ -4292,19 +4292,19 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>1</v>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>5</v>
@@ -4352,25 +4352,25 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="8" t="n">
         <v>5</v>
@@ -4382,25 +4382,25 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>5</v>
@@ -4442,22 +4442,22 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>0</v>
@@ -4472,22 +4472,22 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G122" s="8" t="n">
         <v>1</v>
@@ -4502,25 +4502,25 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="6" t="n">
         <v>5</v>
@@ -4532,25 +4532,25 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
         <v>5</v>
@@ -4622,22 +4622,22 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
         <v>2</v>
@@ -4652,19 +4652,19 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>0</v>
@@ -4712,25 +4712,25 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
         <v>4</v>
@@ -4742,25 +4742,25 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
         <v>4</v>
@@ -4772,25 +4772,25 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="8" t="n">
         <v>4</v>
@@ -4802,22 +4802,22 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>2</v>
@@ -4832,25 +4832,25 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="8" t="n">
         <v>3</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G135" s="6" t="n">
         <v>1</v>
@@ -4892,25 +4892,25 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="8" t="n">
         <v>3</v>
@@ -4922,19 +4922,19 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>0</v>
@@ -4952,22 +4952,22 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="8" t="n">
         <v>1</v>
@@ -4982,22 +4982,22 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>1</v>
@@ -5012,25 +5012,25 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
         <v>3</v>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5057,10 +5057,10 @@
         <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>3</v>
@@ -5072,25 +5072,25 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
         <v>3</v>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5252,16 +5252,16 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="8" t="n">
         <v>1</v>
@@ -5282,16 +5282,16 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="6" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="6" t="n">
         <v>1</v>
@@ -5312,16 +5312,16 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="8" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="8" t="n">
         <v>1</v>
@@ -5342,16 +5342,16 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
         <v>1</v>
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>IESL Kandurata Chapter Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>IESL Kandurata Chapter Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Union Bank Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>TalkCrafters Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D166" s="8" t="n">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>Wennappuwa Toastmasters Club</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>TalkCrafters Toastmasters Club</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D168" s="8" t="n">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D169" s="6" t="n">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>Wennappuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D170" s="8" t="n">
@@ -5947,15 +5947,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5975,947 +5973,709 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pathways Quality EXCELLENCE Leaderboard</t>
+          <t>Clubs Qualifying — Pathways Quality EXCELLENCE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Div-Area</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Div-Area</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Ovation 2027</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>1</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>APIIT Kandy Toastmasters Club</t>
+        </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
           <t>F-03</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>2</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Awakening Toastmasters</t>
+        </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
           <t>C-01</t>
         </is>
       </c>
+      <c r="C8" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>3</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Baurs Toastmasters Club (BTC)</t>
+        </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
           <t>A-02</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="D9" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Braybrooke Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CA Sri Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>CIPM Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Capital Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Central Link Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Ceylinco Life Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Dowels Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Dynamic Avenue Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>HILL CAPITAL TOASTMASTERS</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>HNB Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>HSBC Global Service Centre</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Horana Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Braybrooke Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="D21" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Ja-Ela Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>KDU Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Kadawatha Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Kandy Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Kelaniya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Matale Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Moratuwa Toastmasters</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>NHCO Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>PIM Toastmasters</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Panadura Toastmasters</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Rajagiriya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Ralph Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Silvermill Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Smedley Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Sri Lanka Customs Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>C-04</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="C38" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Startup Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>CIPM Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
+      <c r="D39" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Synopsys Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>The Millennium Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Virtusa Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Capital Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Central Link Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Ceylinco Life Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Dowels Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>HNB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>HSBC Global Service Centre</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Horana Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Ja-Ela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>KDU Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Kadawatha Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Kandy Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Kelaniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Matale Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Moratuwa Toastmasters</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>NHCO Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>PIM Toastmasters</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Panadura Toastmasters</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Rajagiriya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Silvermill Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Smedley Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Startup Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>The Millennium Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
       <c r="D43" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="6" t="inlineStr"/>
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>First 20 clubs (by qualifying date, not shown here) recognized at Ovation 2027. All qualifying clubs recognized on District social media.</t>
+          <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
       </c>
     </row>
@@ -6930,14 +6690,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6957,1056 +6716,907 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pathways Quality STAR Leaderboard</t>
+          <t>Clubs Qualifying — Pathways Quality STAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Div-Area</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Div-Area</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
           <t>Level 3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>1</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AATSL Emerging Toastmasters Club</t>
+        </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
           <t>C-02</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>2</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>AATSL Toastmasters Club</t>
+        </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
           <t>F-02</t>
         </is>
       </c>
+      <c r="C8" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>3</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aitken Spence Toastmasters</t>
+        </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
           <t>I-02</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>4</v>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Anuradhapura Toastmasters Club</t>
+        </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
           <t>G-03</t>
         </is>
       </c>
+      <c r="C10" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="D10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>5</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>BOI Toastmasters Club</t>
+        </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
           <t>A-04</t>
         </is>
       </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Bcis Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CBA Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>CBL Foods Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>CECB Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>CSE Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Central Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Commercial Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Dehiwala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Dialog Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ECU Sri Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Expolanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>GTN Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>IESL Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Bcis Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>IFS Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Kaduwela Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Kandy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Kegalle Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Marketers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Matara Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Minuwangoda Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>NTG Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CBA Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="C34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Nations Toastmasters</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Oasis Toastmasters</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Omega Line</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>CBL Foods Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CECB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>CSE Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>A-04</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="D37" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>PLC Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Peradeniya University Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Ragama Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Readers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Sampath Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Siyane Toastmasters</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>SriLankan Airlines Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>The Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Central Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Commercial Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Dehiwala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
+      <c r="D47" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Tiqri Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Dialog Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Expolanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>GTN Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>IESL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>IFS Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Kaduwela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Kandy Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Kegalle Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Marketers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Matara Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>NTG Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Nations Toastmasters</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Oasis Toastmasters</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>PLC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Peradeniya University Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Readers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Sampath Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Siyane Toastmasters</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>The Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Tiqri Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
       <c r="D48" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>43</v>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Torrington Toastmasters Club</t>
+        </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
           <t>D-02</t>
         </is>
       </c>
+      <c r="C49" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="D49" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E49" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>44</v>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>UOC Toastmasters Club</t>
+        </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
           <t>G-02</t>
         </is>
       </c>
+      <c r="C50" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="D50" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>45</v>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Vavuniya Toastmasters Club</t>
+        </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
           <t>B-04</t>
         </is>
       </c>
+      <c r="C51" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="D51" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>46</v>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Voice Your Dream Toastmasters Club</t>
+        </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
           <t>F-03</t>
         </is>
       </c>
+      <c r="C52" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="D52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E52" s="8" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>47</v>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday 7 Toastmasters Club</t>
+        </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
           <t>B-03</t>
         </is>
       </c>
+      <c r="C53" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>48</v>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>hSenid Toastmasters Club</t>
+        </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
           <t>G-04</t>
         </is>
       </c>
+      <c r="C54" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="D54" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="8" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Clubs achieving Excellence tier are shown only in the Excellence leaderboard, per award rules.</t>
+          <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>454</v>
+        <v>415</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1674</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 164 active clubs (of 174 total).</t>
+          <t>Across 159 active clubs (of 173 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E9" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>35</v>
-      </c>
       <c r="G9" s="6" t="n">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>21</v>
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>15</v>
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>42</v>
-      </c>
       <c r="G11" s="6" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -816,23 +816,23 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17</v>
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>20</v>
-      </c>
       <c r="H7" s="6" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1064,16 +1064,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>5</v>
-      </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1211,19 +1211,19 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>2</v>
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>2</v>
@@ -1403,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -1577,13 +1577,13 @@
         <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -1817,13 +1817,13 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="F34" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1892,16 +1892,16 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>4</v>
@@ -1910,10 +1910,10 @@
         <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1922,16 +1922,16 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>4</v>
@@ -1940,10 +1940,10 @@
         <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -2102,25 +2102,25 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -2192,22 +2192,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>2</v>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
@@ -2243,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -2282,16 +2282,16 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>4</v>
@@ -2303,7 +2303,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -2342,28 +2342,28 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -2402,16 +2402,16 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>4</v>
@@ -2423,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2</v>
@@ -2453,7 +2453,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
@@ -2477,13 +2477,13 @@
         <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -2492,28 +2492,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E56" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="H56" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -2627,10 +2627,10 @@
         <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>13</v>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -2657,10 +2657,10 @@
         <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" s="6" t="n">
         <v>13</v>
@@ -2672,16 +2672,16 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2717,13 +2717,13 @@
         <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -2750,10 +2750,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2780,10 +2780,10 @@
         <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2810,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
@@ -2837,13 +2837,13 @@
         <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -2852,16 +2852,16 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>4</v>
@@ -2873,7 +2873,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2900,10 +2900,10 @@
         <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -2987,10 +2987,10 @@
         <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>12</v>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
@@ -3152,19 +3152,19 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" s="8" t="n">
         <v>2</v>
@@ -3173,7 +3173,7 @@
         <v>2</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -3200,10 +3200,10 @@
         <v>2</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
@@ -3212,28 +3212,28 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
@@ -3272,19 +3272,19 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" s="8" t="n">
         <v>2</v>
@@ -3293,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -3302,28 +3302,28 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -3362,28 +3362,28 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -3392,19 +3392,19 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="8" t="n">
         <v>2</v>
@@ -3413,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -3452,28 +3452,28 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
@@ -3542,16 +3542,16 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>2</v>
@@ -3560,10 +3560,10 @@
         <v>2</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -3572,28 +3572,28 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -3632,28 +3632,28 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
@@ -3680,10 +3680,10 @@
         <v>1</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -3692,25 +3692,25 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="8" t="n">
         <v>8</v>
@@ -3722,19 +3722,19 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>0</v>
@@ -3752,28 +3752,28 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -3782,16 +3782,16 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>2</v>
@@ -3800,10 +3800,10 @@
         <v>1</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -3812,25 +3812,25 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
         <v>7</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3857,10 +3857,10 @@
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>7</v>
@@ -3872,22 +3872,22 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>1</v>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
@@ -3920,10 +3920,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -3932,28 +3932,28 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -3962,28 +3962,28 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -3992,19 +3992,19 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -4022,25 +4022,25 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>6</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>1</v>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
         <v>6</v>
@@ -4082,25 +4082,25 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H109" s="6" t="n">
         <v>6</v>
@@ -4112,25 +4112,25 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="8" t="n">
         <v>6</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>1</v>
@@ -4163,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4217,13 +4217,13 @@
         <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -4232,28 +4232,28 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -4262,28 +4262,28 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -4292,25 +4292,25 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E116" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" s="8" t="n">
         <v>5</v>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>5</v>
@@ -4352,28 +4352,28 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
@@ -4382,28 +4382,28 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
@@ -4412,28 +4412,28 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -4442,28 +4442,28 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -4502,28 +4502,28 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>1</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -4562,28 +4562,28 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -4592,25 +4592,25 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
         <v>4</v>
@@ -4622,28 +4622,28 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -4652,28 +4652,28 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -4682,28 +4682,28 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4712,28 +4712,28 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4742,28 +4742,28 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4772,28 +4772,28 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4802,19 +4802,19 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         <v>2</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
         <v>3</v>
@@ -4862,19 +4862,19 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
@@ -4892,22 +4892,22 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>0</v>
@@ -4922,16 +4922,16 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>1</v>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -4952,28 +4952,28 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -4982,28 +4982,28 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -5012,28 +5012,28 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -5072,19 +5072,19 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -5102,16 +5102,16 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5120,10 +5120,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5147,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -5162,28 +5162,28 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -5192,28 +5192,28 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -5222,19 +5222,19 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>0</v>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5270,10 +5270,10 @@
         <v>0</v>
       </c>
       <c r="G148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5300,10 +5300,10 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -5312,16 +5312,16 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="8" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -5342,16 +5342,16 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>IESL Kandurata Chapter Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
@@ -5783,156 +5783,6 @@
         <v>0</v>
       </c>
       <c r="H165" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>SLT Toastmasters</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="n">
-        <v>161</v>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>162</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>TalkCrafters Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="n">
-        <v>163</v>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>Union Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>E-04</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="n">
-        <v>164</v>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Wennappuwa Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5973,7 +5823,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6081,16 +5931,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>3</v>
@@ -6099,34 +5949,34 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -6135,52 +5985,52 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>KDU Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>3</v>
@@ -6189,70 +6039,70 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>3</v>
@@ -6261,106 +6111,106 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>KDU Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>3</v>
@@ -6369,106 +6219,106 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>3</v>
@@ -6477,48 +6327,48 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -6531,52 +6381,52 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>3</v>
@@ -6585,12 +6435,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -6603,16 +6453,16 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>3</v>
@@ -6621,52 +6471,52 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>3</v>
@@ -6716,7 +6566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6710,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -6878,16 +6728,16 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6896,16 +6746,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6914,16 +6764,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6932,16 +6782,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6950,16 +6800,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6968,7 +6818,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -6977,7 +6827,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>2</v>
@@ -6986,16 +6836,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -7004,16 +6854,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -7022,16 +6872,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -7040,16 +6890,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -7058,16 +6908,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -7076,16 +6926,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -7094,16 +6944,16 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -7112,12 +6962,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -7130,12 +6980,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -7148,16 +6998,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>2</v>
@@ -7166,12 +7016,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -7184,12 +7034,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -7202,16 +7052,16 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
@@ -7220,12 +7070,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -7238,12 +7088,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -7256,16 +7106,16 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>2</v>
@@ -7274,16 +7124,16 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2</v>
@@ -7292,16 +7142,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
@@ -7310,16 +7160,16 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2</v>
@@ -7328,16 +7178,16 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>2</v>
@@ -7346,12 +7196,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7364,12 +7214,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -7382,12 +7232,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7400,12 +7250,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -7418,16 +7268,16 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -7436,16 +7286,16 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>2</v>
@@ -7454,16 +7304,16 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
@@ -7472,16 +7322,16 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
@@ -7490,16 +7340,16 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>2</v>
@@ -7508,30 +7358,30 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -7544,52 +7394,52 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" s="6" t="n">
         <v>2</v>
@@ -7598,19 +7448,19 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,19 +554,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1537</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="9">
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -689,10 +689,10 @@
         <v>39</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>17</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>54</v>
@@ -720,7 +720,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -739,7 +739,7 @@
         <v>77</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>28</v>
@@ -748,7 +748,7 @@
         <v>33</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>21</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>56</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>15</v>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>47</v>
@@ -804,7 +804,7 @@
         <v>27</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>18</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>39</v>
@@ -832,7 +832,7 @@
         <v>39</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>40</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>23</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>19</v>
@@ -882,13 +882,13 @@
         <v>42</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17</v>
@@ -907,16 +907,16 @@
         <v>39</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>28</v>
-      </c>
       <c r="G15" s="6" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>17</v>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1142,25 +1142,25 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>20</v>
@@ -1172,16 +1172,16 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
@@ -1190,7 +1190,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>20</v>
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -1232,25 +1232,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>19</v>
@@ -1382,25 +1382,25 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>18</v>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>18</v>
@@ -1442,16 +1442,16 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>5</v>
@@ -1460,7 +1460,7 @@
         <v>3</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>18</v>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="F22" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>18</v>
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1532,25 +1532,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>17</v>
@@ -1562,25 +1562,25 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>17</v>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>17</v>
@@ -1682,22 +1682,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>3</v>
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1742,16 +1742,16 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>4</v>
@@ -1760,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>16</v>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>16</v>
@@ -1802,16 +1802,16 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>16</v>
@@ -1832,19 +1832,19 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
@@ -2372,19 +2372,19 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>3</v>
@@ -2402,28 +2402,28 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E53" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F53" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2</v>
@@ -2462,25 +2462,25 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>13</v>
@@ -2492,25 +2492,25 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>13</v>
@@ -2522,22 +2522,22 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="n">
         <v>2</v>
@@ -2552,22 +2552,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>2</v>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
@@ -2597,10 +2597,10 @@
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>13</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -2642,25 +2642,25 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6" t="n">
         <v>13</v>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -2987,10 +2987,10 @@
         <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>12</v>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>2</v>
@@ -3143,7 +3143,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>2</v>
@@ -3182,25 +3182,25 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79" s="6" t="n">
         <v>11</v>
@@ -3212,22 +3212,22 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2</v>
@@ -3242,19 +3242,19 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>1</v>
@@ -3272,22 +3272,22 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>2</v>
@@ -3302,28 +3302,28 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
@@ -3332,25 +3332,25 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="8" t="n">
         <v>10</v>
@@ -3362,22 +3362,22 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
@@ -3392,19 +3392,19 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="n">
         <v>2</v>
@@ -3413,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
@@ -3452,16 +3452,16 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="8" t="n">
         <v>2</v>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
         <v>9</v>
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -3542,25 +3542,25 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>8</v>
@@ -3572,25 +3572,25 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="8" t="n">
         <v>8</v>
@@ -3602,25 +3602,25 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>8</v>
@@ -3632,12 +3632,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
@@ -3662,22 +3662,22 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>1</v>
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -3722,19 +3722,19 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -3752,25 +3752,25 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="8" t="n">
         <v>7</v>
@@ -3782,25 +3782,25 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
         <v>7</v>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
         <v>7</v>
@@ -3842,25 +3842,25 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>7</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>2</v>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="8" t="n">
         <v>7</v>
@@ -5823,7 +5823,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6237,16 +6237,16 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>3</v>
@@ -6255,16 +6255,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>3</v>
@@ -6273,16 +6273,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>3</v>
@@ -6566,7 +6566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6710,16 +6710,16 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
@@ -6728,16 +6728,16 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6746,16 +6746,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6764,16 +6764,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6782,16 +6782,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6800,16 +6800,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6818,16 +6818,16 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>2</v>
@@ -6836,16 +6836,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -6854,16 +6854,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -6872,16 +6872,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -6890,12 +6890,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -6908,16 +6908,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -6926,16 +6926,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -6944,16 +6944,16 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -6962,16 +6962,16 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>2</v>
@@ -6980,16 +6980,16 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>2</v>
@@ -6998,16 +6998,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>2</v>
@@ -7016,16 +7016,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -7034,12 +7034,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -7052,12 +7052,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -7070,12 +7070,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -7088,16 +7088,16 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>2</v>
@@ -7106,12 +7106,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -7124,16 +7124,16 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2</v>
@@ -7142,16 +7142,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
@@ -7160,12 +7160,12 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -7178,12 +7178,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -7196,12 +7196,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7214,12 +7214,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -7232,12 +7232,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7250,16 +7250,16 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
@@ -7268,16 +7268,16 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -7286,16 +7286,16 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>2</v>
@@ -7304,16 +7304,16 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
@@ -7322,16 +7322,16 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
@@ -7340,73 +7340,73 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Clubs Qualifying — Pathways " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Clubs Qualifying — Pathway_2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Pathways " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Pathway_2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1524</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 159 active clubs (of 173 total).</t>
+          <t>Across 164 active clubs (of 174 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>21</v>
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>15</v>
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -816,23 +816,23 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E13" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>168</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>20</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>148</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17</v>
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1064,16 +1064,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -1187,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>2</v>
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1430,10 +1430,10 @@
         <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>4</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         <v>4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1574,16 +1574,16 @@
         <v>7</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>3</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1892,16 +1892,16 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>4</v>
@@ -1910,10 +1910,10 @@
         <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
@@ -1922,16 +1922,16 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>4</v>
@@ -1940,10 +1940,10 @@
         <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2102,25 +2102,25 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -2192,22 +2192,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
         <v>2</v>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
@@ -2243,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2282,16 +2282,16 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>4</v>
@@ -2303,7 +2303,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2342,28 +2342,28 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
@@ -2387,13 +2387,13 @@
         <v>4</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2402,28 +2402,28 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2</v>
@@ -2453,7 +2453,7 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -2462,28 +2462,28 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -2492,28 +2492,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E56" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -2552,22 +2552,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>2</v>
@@ -2582,16 +2582,16 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>4</v>
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>13</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -2627,10 +2627,10 @@
         <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>13</v>
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>3</v>
@@ -2672,16 +2672,16 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2717,13 +2717,13 @@
         <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -2750,10 +2750,10 @@
         <v>2</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2780,10 +2780,10 @@
         <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2810,10 +2810,10 @@
         <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
@@ -2837,13 +2837,13 @@
         <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -2852,16 +2852,16 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>4</v>
@@ -2873,7 +2873,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2900,10 +2900,10 @@
         <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>2</v>
@@ -3143,7 +3143,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -3182,28 +3182,28 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
@@ -3212,19 +3212,19 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" s="8" t="n">
         <v>2</v>
@@ -3233,7 +3233,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
@@ -3242,28 +3242,28 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
@@ -3272,28 +3272,28 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -3314,7 +3314,7 @@
         <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>2</v>
@@ -3323,7 +3323,7 @@
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E84" s="8" t="n">
         <v>4</v>
@@ -3353,7 +3353,7 @@
         <v>2</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -3362,28 +3362,28 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -3392,19 +3392,19 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="8" t="n">
         <v>2</v>
@@ -3413,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -3452,28 +3452,28 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
@@ -3482,28 +3482,28 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -3542,28 +3542,28 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -3572,19 +3572,19 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="8" t="n">
         <v>2</v>
@@ -3593,7 +3593,7 @@
         <v>2</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -3632,28 +3632,28 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -3662,28 +3662,28 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -3692,28 +3692,28 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -3722,16 +3722,16 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>3</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -3752,28 +3752,28 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
@@ -3797,13 +3797,13 @@
         <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -3812,22 +3812,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
@@ -3842,22 +3842,22 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>1</v>
@@ -3872,25 +3872,25 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
         <v>7</v>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
@@ -3920,10 +3920,10 @@
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3932,28 +3932,28 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3962,28 +3962,28 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3992,19 +3992,19 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>0</v>
@@ -4013,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -4022,25 +4022,25 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>6</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>1</v>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" s="8" t="n">
         <v>6</v>
@@ -4082,25 +4082,25 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6" t="n">
         <v>6</v>
@@ -4112,25 +4112,25 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="8" t="n">
         <v>6</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -4154,7 +4154,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>1</v>
@@ -4163,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
@@ -4172,28 +4172,28 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4217,13 +4217,13 @@
         <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -4232,28 +4232,28 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
@@ -4262,28 +4262,28 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -4292,25 +4292,25 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E116" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
         <v>5</v>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>5</v>
@@ -4352,28 +4352,28 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -4382,28 +4382,28 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -4412,28 +4412,28 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -4442,28 +4442,28 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -4472,28 +4472,28 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -4502,28 +4502,28 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>1</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -4562,28 +4562,28 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -4592,25 +4592,25 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
         <v>4</v>
@@ -4622,28 +4622,28 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -4652,28 +4652,28 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
@@ -4682,28 +4682,28 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -4712,28 +4712,28 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
@@ -4742,28 +4742,28 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -4772,28 +4772,28 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -4802,19 +4802,19 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         <v>2</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
@@ -4847,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" s="8" t="n">
         <v>3</v>
@@ -4862,19 +4862,19 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
@@ -4892,22 +4892,22 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>0</v>
@@ -4922,16 +4922,16 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>1</v>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -4952,28 +4952,28 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -4982,28 +4982,28 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -5012,28 +5012,28 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -5042,28 +5042,28 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -5072,19 +5072,19 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="8" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -5102,16 +5102,16 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5120,10 +5120,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5147,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -5162,28 +5162,28 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -5192,28 +5192,28 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -5222,19 +5222,19 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>0</v>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5270,10 +5270,10 @@
         <v>0</v>
       </c>
       <c r="G148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5300,10 +5300,10 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -5312,16 +5312,16 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="8" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -5342,16 +5342,16 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>IESL Kandurata Chapter Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Puttalam Toastmasters</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5762,27 +5762,177 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
+          <t>Rizing Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>SLT Toastmasters</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Serendib 7 Star Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>TalkCrafters Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
           <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="D165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="6" t="n">
+      <c r="D169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Wennappuwa Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5823,7 +5973,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5931,16 +6081,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>3</v>
@@ -5949,34 +6099,34 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -5985,52 +6135,52 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>KDU Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>3</v>
@@ -6039,70 +6189,70 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>3</v>
@@ -6111,106 +6261,106 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>KDU Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>3</v>
@@ -6219,106 +6369,106 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>3</v>
@@ -6327,48 +6477,48 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -6381,52 +6531,52 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>3</v>
@@ -6435,12 +6585,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -6453,16 +6603,16 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>3</v>
@@ -6471,52 +6621,52 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>3</v>
@@ -6566,7 +6716,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6710,16 +6860,16 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
@@ -6728,16 +6878,16 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6746,16 +6896,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6764,16 +6914,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6782,16 +6932,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6800,16 +6950,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6818,16 +6968,16 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>2</v>
@@ -6836,16 +6986,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -6854,16 +7004,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -6872,12 +7022,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -6890,16 +7040,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -6908,16 +7058,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -6926,16 +7076,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -6944,16 +7094,16 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -6962,16 +7112,16 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>2</v>
@@ -6980,16 +7130,16 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>2</v>
@@ -6998,16 +7148,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>2</v>
@@ -7016,16 +7166,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -7034,12 +7184,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -7052,16 +7202,16 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
@@ -7070,12 +7220,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -7088,16 +7238,16 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>2</v>
@@ -7106,16 +7256,16 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>2</v>
@@ -7124,16 +7274,16 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2</v>
@@ -7142,16 +7292,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
@@ -7160,16 +7310,16 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2</v>
@@ -7178,16 +7328,16 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>2</v>
@@ -7196,12 +7346,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7214,7 +7364,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -7232,12 +7382,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7250,16 +7400,16 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
@@ -7268,16 +7418,16 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -7286,16 +7436,16 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>2</v>
@@ -7304,12 +7454,12 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -7322,16 +7472,16 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
@@ -7340,34 +7490,34 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>2</v>
@@ -7376,34 +7526,34 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>2</v>
@@ -7412,34 +7562,34 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D53" s="6" t="n">
         <v>2</v>
@@ -7448,19 +7598,19 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1142,25 +1142,25 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>21</v>
@@ -1172,25 +1172,25 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>21</v>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>21</v>
@@ -1232,25 +1232,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>21</v>
@@ -1322,25 +1322,25 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>19</v>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>19</v>
@@ -1382,25 +1382,25 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>19</v>
@@ -1412,19 +1412,19 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>3</v>
@@ -1442,25 +1442,25 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>19</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1514,13 +1514,13 @@
         <v>6</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>19</v>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>18</v>
@@ -1562,25 +1562,25 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>18</v>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
@@ -1622,16 +1622,16 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>4</v>
@@ -1640,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>18</v>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>18</v>
@@ -1682,22 +1682,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>8</v>
-      </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>2</v>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2</v>
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>3</v>
@@ -1772,25 +1772,25 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>18</v>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>17</v>
@@ -1832,22 +1832,22 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>3</v>
@@ -1862,16 +1862,16 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>4</v>
@@ -1880,7 +1880,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35" s="6" t="n">
         <v>17</v>
@@ -1892,22 +1892,22 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>3</v>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>3</v>
@@ -1952,25 +1952,25 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>17</v>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>3</v>
@@ -2042,22 +2042,22 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>2</v>
@@ -2072,22 +2072,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2</v>
@@ -2102,25 +2102,25 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2132,25 +2132,25 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>15</v>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>15</v>
@@ -2192,16 +2192,16 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>15</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>2</v>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>15</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
@@ -2297,10 +2297,10 @@
         <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>15</v>
@@ -2312,25 +2312,25 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>15</v>
@@ -2342,25 +2342,25 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>15</v>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>15</v>
@@ -2402,16 +2402,16 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>4</v>
@@ -2420,7 +2420,7 @@
         <v>3</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>15</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>2</v>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
@@ -2477,10 +2477,10 @@
         <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>14</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -2501,16 +2501,16 @@
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>14</v>
@@ -2552,22 +2552,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>2</v>
@@ -2578,26 +2578,26 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
@@ -2608,16 +2608,16 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -2638,26 +2638,26 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>2</v>
@@ -2668,20 +2668,20 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>4</v>
@@ -2690,7 +2690,7 @@
         <v>2</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>13</v>
@@ -2698,16 +2698,16 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2717,10 +2717,10 @@
         <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>13</v>
@@ -2728,20 +2728,20 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64" s="8" t="n">
         <v>4</v>
@@ -2750,7 +2750,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>13</v>
@@ -2758,16 +2758,16 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2777,10 +2777,10 @@
         <v>4</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="n">
         <v>13</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
@@ -2818,26 +2818,26 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>2</v>
@@ -2848,16 +2848,16 @@
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
@@ -2878,16 +2878,16 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2908,16 +2908,16 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -2938,16 +2938,16 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -2968,26 +2968,26 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>2</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3028,16 +3028,16 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3058,16 +3058,16 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3088,16 +3088,16 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
@@ -3118,16 +3118,16 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
@@ -3148,16 +3148,16 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
@@ -3178,16 +3178,16 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -3208,16 +3208,16 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
@@ -3238,16 +3238,16 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -3268,16 +3268,16 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
@@ -3298,16 +3298,16 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
@@ -3328,16 +3328,16 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
@@ -3358,26 +3358,26 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
@@ -3388,26 +3388,26 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2</v>
@@ -3418,29 +3418,29 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>11</v>
@@ -3448,26 +3448,26 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
         <v>2</v>
@@ -3478,29 +3478,29 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H89" s="6" t="n">
         <v>11</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
@@ -3568,26 +3568,26 @@
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E92" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>2</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
@@ -3628,26 +3628,26 @@
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="n">
         <v>2</v>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
@@ -3688,26 +3688,26 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="8" t="n">
         <v>1</v>
@@ -3718,29 +3718,29 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6" t="n">
         <v>8</v>
@@ -3748,29 +3748,29 @@
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
         <v>8</v>
@@ -3778,26 +3778,26 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>1</v>
@@ -3808,29 +3808,29 @@
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="8" t="n">
         <v>7</v>
@@ -3838,11 +3838,11 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3857,10 +3857,10 @@
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>7</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
@@ -3917,10 +3917,10 @@
         <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" s="6" t="n">
         <v>7</v>
@@ -3928,29 +3928,29 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
         <v>7</v>
@@ -3958,29 +3958,29 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
         <v>7</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
@@ -4018,29 +4018,29 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>6</v>
@@ -4048,29 +4048,29 @@
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="8" t="n">
         <v>6</v>
@@ -4078,26 +4078,26 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G109" s="6" t="n">
         <v>0</v>
@@ -4108,29 +4108,29 @@
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110" s="8" t="n">
         <v>6</v>
@@ -4138,29 +4138,29 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6" t="n">
         <v>6</v>
@@ -4168,29 +4168,29 @@
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H112" s="8" t="n">
         <v>6</v>
@@ -4198,26 +4198,26 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>0</v>
@@ -4228,29 +4228,29 @@
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
         <v>6</v>
@@ -4258,29 +4258,29 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
         <v>6</v>
@@ -4288,16 +4288,16 @@
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
@@ -4307,10 +4307,10 @@
         <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" s="8" t="n">
         <v>5</v>
@@ -4318,29 +4318,29 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>5</v>
@@ -4348,7 +4348,7 @@
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
@@ -4378,29 +4378,29 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>5</v>
@@ -4408,29 +4408,29 @@
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
         <v>5</v>
@@ -4438,29 +4438,29 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="6" t="n">
         <v>5</v>
@@ -4468,29 +4468,29 @@
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="8" t="n">
         <v>5</v>
@@ -4498,29 +4498,29 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
         <v>5</v>
@@ -4528,26 +4528,26 @@
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>0</v>
@@ -4558,26 +4558,26 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G125" s="6" t="n">
         <v>2</v>
@@ -4588,29 +4588,29 @@
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="8" t="n">
         <v>4</v>
@@ -4618,29 +4618,29 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
         <v>4</v>
@@ -4648,29 +4648,29 @@
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="8" t="n">
         <v>4</v>
@@ -4678,29 +4678,29 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6" t="n">
         <v>4</v>
@@ -4708,26 +4708,26 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
@@ -4768,29 +4768,29 @@
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
         <v>4</v>
@@ -4798,29 +4798,29 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
         <v>4</v>
@@ -4828,29 +4828,29 @@
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
         <v>3</v>
@@ -4858,23 +4858,23 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
@@ -4918,29 +4918,29 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>3</v>
@@ -4948,29 +4948,29 @@
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
         <v>3</v>
@@ -4978,29 +4978,29 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
         <v>3</v>
@@ -5008,23 +5008,23 @@
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
@@ -5038,16 +5038,16 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5057,10 +5057,10 @@
         <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>3</v>
@@ -5068,11 +5068,11 @@
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
@@ -5081,13 +5081,13 @@
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G142" s="8" t="n">
         <v>1</v>
@@ -5098,20 +5098,20 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>2</v>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
@@ -5188,20 +5188,20 @@
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="8" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" s="8" t="n">
         <v>2</v>
@@ -5218,16 +5218,16 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,20 +5248,20 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="8" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
@@ -5308,20 +5308,20 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="8" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="8" t="n">
         <v>1</v>
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,7 +5368,7 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
     </row>
     <row r="170">
       <c r="A170" s="7" t="n">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Pathways " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Pathway_2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="District-Wide Level Totals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Division Leaderboard (Total " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Club Leaderboard — District-" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clubs Qualifying — Pathways " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Clubs Qualifying — Pathway_2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>616</v>
+        <v>556</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1674</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 164 active clubs (of 174 total).</t>
+          <t>Across 158 active clubs (of 173 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>21</v>
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -816,23 +816,23 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17</v>
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>20</v>
-      </c>
       <c r="H7" s="6" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1064,16 +1064,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1322,25 +1322,25 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>19</v>
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1382,19 +1382,19 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1532,16 +1532,16 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>5</v>
@@ -1550,10 +1550,10 @@
         <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>5</v>
-      </c>
       <c r="F25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>3</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1952,16 +1952,16 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1982,16 +1982,16 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>4</v>
@@ -2000,10 +2000,10 @@
         <v>2</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
@@ -2027,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -2102,16 +2102,16 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>6</v>
@@ -2120,7 +2120,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2147,13 +2147,13 @@
         <v>4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -2162,19 +2162,19 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2</v>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -2192,16 +2192,16 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
@@ -2210,10 +2210,10 @@
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -2222,28 +2222,28 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
@@ -2270,10 +2270,10 @@
         <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -2282,28 +2282,28 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
@@ -2327,13 +2327,13 @@
         <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -2342,28 +2342,28 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -2372,16 +2372,16 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>4</v>
@@ -2393,7 +2393,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
@@ -2420,15 +2420,15 @@
         <v>3</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
         <v>4</v>
@@ -2453,58 +2453,58 @@
         <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>2</v>
@@ -2513,51 +2513,51 @@
         <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
@@ -2567,10 +2567,10 @@
         <v>4</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>13</v>
@@ -2578,26 +2578,26 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
@@ -2608,16 +2608,16 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
@@ -2627,10 +2627,10 @@
         <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>13</v>
@@ -2638,23 +2638,23 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>2</v>
@@ -2663,21 +2663,21 @@
         <v>2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
@@ -2690,24 +2690,24 @@
         <v>2</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2720,28 +2720,28 @@
         <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" s="8" t="n">
         <v>4</v>
@@ -2753,21 +2753,21 @@
         <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2777,27 +2777,27 @@
         <v>4</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2810,28 +2810,28 @@
         <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>4</v>
@@ -2843,25 +2843,25 @@
         <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68" s="8" t="n">
         <v>4</v>
@@ -2873,21 +2873,21 @@
         <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2900,19 +2900,19 @@
         <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -2938,16 +2938,16 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -2968,26 +2968,26 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>2</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3028,16 +3028,16 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3058,16 +3058,16 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3088,53 +3088,53 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>2</v>
@@ -3143,12 +3143,12 @@
         <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         <v>2</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -3191,19 +3191,19 @@
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
@@ -3212,28 +3212,28 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -3242,16 +3242,16 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>4</v>
@@ -3263,28 +3263,28 @@
         <v>2</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F82" s="8" t="n">
         <v>2</v>
@@ -3293,28 +3293,28 @@
         <v>2</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>2</v>
@@ -3323,265 +3323,265 @@
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92" s="8" t="n">
         <v>2</v>
@@ -3590,54 +3590,54 @@
         <v>3</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
@@ -3647,82 +3647,82 @@
         <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -3734,115 +3734,115 @@
         <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3857,18 +3857,18 @@
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>0</v>
@@ -3893,328 +3893,328 @@
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
@@ -4223,88 +4223,88 @@
         <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
@@ -4313,106 +4313,106 @@
         <v>2</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -4421,67 +4421,67 @@
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" s="8" t="n">
         <v>1</v>
@@ -4490,31 +4490,31 @@
         <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
@@ -4523,81 +4523,81 @@
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
@@ -4607,112 +4607,112 @@
         <v>1</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>Informatics Institute of Technology</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
@@ -4727,91 +4727,91 @@
         <v>1</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>0</v>
@@ -4820,31 +4820,31 @@
         <v>0</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
@@ -4853,21 +4853,21 @@
         <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
@@ -4880,91 +4880,91 @@
         <v>0</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -4973,81 +4973,81 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5057,87 +5057,87 @@
         <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5147,27 +5147,27 @@
         <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5177,31 +5177,31 @@
         <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="8" t="n">
         <v>0</v>
@@ -5210,24 +5210,24 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,20 +5248,20 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>0</v>
@@ -5273,21 +5273,21 @@
         <v>0</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5300,24 +5300,24 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5330,28 +5330,28 @@
         <v>0</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>IESL Kandurata Chapter Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5753,186 +5753,6 @@
         <v>0</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>Rizing Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B166" s="8" t="inlineStr">
-        <is>
-          <t>SLT Toastmasters</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B168" s="8" t="inlineStr">
-        <is>
-          <t>TalkCrafters Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>Union Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>E-04</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="n">
-        <v>132</v>
-      </c>
-      <c r="B170" s="8" t="inlineStr">
-        <is>
-          <t>Wennappuwa Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5973,7 +5793,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6081,16 +5901,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CA Sri Lanka Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>3</v>
@@ -6099,34 +5919,34 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -6135,52 +5955,52 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>KDU Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>3</v>
@@ -6189,70 +6009,70 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>3</v>
@@ -6261,84 +6081,84 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>KDU Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -6351,34 +6171,34 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>3</v>
@@ -6387,30 +6207,30 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -6423,52 +6243,52 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>3</v>
@@ -6477,48 +6297,48 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
@@ -6531,52 +6351,52 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>3</v>
@@ -6585,12 +6405,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -6603,16 +6423,16 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>3</v>
@@ -6621,52 +6441,52 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>3</v>
@@ -6716,7 +6536,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6860,16 +6680,16 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
@@ -6878,16 +6698,16 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6896,16 +6716,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6914,16 +6734,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6932,16 +6752,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6950,16 +6770,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6968,16 +6788,16 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>2</v>
@@ -6986,16 +6806,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -7004,16 +6824,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -7022,12 +6842,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -7040,16 +6860,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -7058,16 +6878,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -7076,16 +6896,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -7094,16 +6914,16 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -7112,16 +6932,16 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>2</v>
@@ -7130,16 +6950,16 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>2</v>
@@ -7148,16 +6968,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>2</v>
@@ -7166,16 +6986,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -7184,12 +7004,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -7202,16 +7022,16 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
@@ -7220,12 +7040,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -7238,16 +7058,16 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>2</v>
@@ -7256,16 +7076,16 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>2</v>
@@ -7274,16 +7094,16 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2</v>
@@ -7292,16 +7112,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
@@ -7310,16 +7130,16 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2</v>
@@ -7328,16 +7148,16 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>2</v>
@@ -7346,12 +7166,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7364,7 +7184,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -7382,12 +7202,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7400,16 +7220,16 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
@@ -7418,16 +7238,16 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -7436,16 +7256,16 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>2</v>
@@ -7454,12 +7274,12 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -7472,16 +7292,16 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>2</v>
@@ -7490,34 +7310,34 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>2</v>
@@ -7526,34 +7346,34 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>2</v>
@@ -7562,34 +7382,34 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" s="6" t="n">
         <v>2</v>
@@ -7598,19 +7418,19 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>556</v>
+        <v>589</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1472</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 158 active clubs (of 173 total).</t>
+          <t>Across 159 active clubs (of 173 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>48</v>
-      </c>
       <c r="G7" s="6" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>17</v>
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>17</v>
@@ -736,19 +736,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>28</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>21</v>
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -820,19 +820,19 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>23</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>19</v>
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17</v>
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>17</v>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1130,10 +1130,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1142,25 +1142,25 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>20</v>
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1232,25 +1232,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>19</v>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>19</v>
@@ -1292,25 +1292,25 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>19</v>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>18</v>
@@ -1382,22 +1382,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>2</v>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>18</v>
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1502,16 +1502,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>4</v>
@@ -1520,10 +1520,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1532,25 +1532,25 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>17</v>
@@ -1562,19 +1562,19 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>2</v>
@@ -1592,19 +1592,19 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>2</v>
@@ -1618,29 +1618,29 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>17</v>
@@ -1648,26 +1648,26 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="n">
         <v>3</v>
@@ -1678,46 +1678,46 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
@@ -1730,28 +1730,28 @@
         <v>2</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>4</v>
@@ -1760,7 +1760,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>16</v>
@@ -1768,16 +1768,16 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
@@ -1798,29 +1798,29 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>16</v>
@@ -1828,89 +1828,89 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>15</v>
@@ -1918,20 +1918,20 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>4</v>
@@ -1940,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>15</v>
@@ -1948,20 +1948,20 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>4</v>
@@ -1970,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>15</v>
@@ -1978,16 +1978,16 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -2008,26 +2008,26 @@
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2</v>
@@ -2038,29 +2038,29 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>15</v>
@@ -2068,20 +2068,20 @@
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E42" s="8" t="n">
         <v>4</v>
@@ -2090,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>15</v>
@@ -2098,29 +2098,29 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>15</v>
@@ -2128,20 +2128,20 @@
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>4</v>
@@ -2153,28 +2153,28 @@
         <v>2</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2</v>
@@ -2183,51 +2183,51 @@
         <v>3</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
@@ -2248,16 +2248,16 @@
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
@@ -2278,16 +2278,16 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
@@ -2308,16 +2308,16 @@
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
@@ -2327,10 +2327,10 @@
         <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>14</v>
@@ -2338,29 +2338,29 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>14</v>
@@ -2368,16 +2368,16 @@
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
@@ -2398,20 +2398,20 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>4</v>
@@ -2423,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
@@ -2458,29 +2458,29 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>13</v>
@@ -2488,29 +2488,29 @@
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>13</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
@@ -2612,25 +2612,25 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>13</v>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -2660,24 +2660,24 @@
         <v>2</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
@@ -2758,16 +2758,16 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
@@ -2788,16 +2788,16 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
@@ -2878,16 +2878,16 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2908,16 +2908,16 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -2968,26 +2968,26 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="n">
         <v>2</v>
@@ -2998,16 +2998,16 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
@@ -3028,16 +3028,16 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
@@ -3047,10 +3047,10 @@
         <v>4</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>12</v>
@@ -3058,16 +3058,16 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
@@ -3088,53 +3088,53 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>2</v>
@@ -3143,34 +3143,34 @@
         <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" s="8" t="n">
         <v>11</v>
@@ -3178,26 +3178,26 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>2</v>
@@ -3208,149 +3208,149 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
         <v>10</v>
@@ -3358,83 +3358,83 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>2</v>
@@ -3443,25 +3443,25 @@
         <v>2</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
         <v>2</v>
@@ -3470,88 +3470,88 @@
         <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="6" t="n">
         <v>2</v>
@@ -3560,358 +3560,358 @@
         <v>1</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E101" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E103" s="6" t="n">
         <v>1</v>
@@ -3920,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" s="6" t="n">
         <v>6</v>
@@ -3928,83 +3928,83 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>1</v>
@@ -4013,67 +4013,67 @@
         <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -4082,28 +4082,28 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>1</v>
@@ -4133,7 +4133,7 @@
         <v>3</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -4142,22 +4142,22 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G111" s="6" t="n">
         <v>1</v>
@@ -4172,25 +4172,25 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H112" s="8" t="n">
         <v>5</v>
@@ -4198,29 +4198,29 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>5</v>
@@ -4228,113 +4228,113 @@
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E115" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>0</v>
@@ -4343,34 +4343,34 @@
         <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
         <v>4</v>
@@ -4378,29 +4378,29 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>4</v>
@@ -4408,23 +4408,23 @@
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
         <v>0</v>
@@ -4438,209 +4438,209 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6" t="n">
         <v>3</v>
@@ -4648,20 +4648,20 @@
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" s="8" t="n">
         <v>1</v>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
         <v>3</v>
@@ -4678,16 +4678,16 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -4708,26 +4708,26 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Informatics Institute of Technology</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
@@ -4738,26 +4738,26 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
         <v>1</v>
@@ -4768,29 +4768,29 @@
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E132" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
         <v>3</v>
@@ -4798,106 +4798,106 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G134" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4907,40 +4907,40 @@
         <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>2</v>
@@ -4948,23 +4948,23 @@
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -4978,26 +4978,26 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>0</v>
@@ -5008,26 +5008,26 @@
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>0</v>
@@ -5038,20 +5038,20 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="6" t="n">
         <v>1</v>
@@ -5063,28 +5063,28 @@
         <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="8" t="n">
         <v>0</v>
@@ -5098,23 +5098,23 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>0</v>
@@ -5128,29 +5128,29 @@
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
         <v>1</v>
@@ -5158,16 +5158,16 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5188,20 +5188,20 @@
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="8" t="n">
         <v>0</v>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="8" t="n">
         <v>1</v>
@@ -5218,16 +5218,16 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,16 +5668,16 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5698,16 +5698,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5728,31 +5728,61 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
+          <t>Serendib 7 Star Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
           <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="D164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" s="8" t="n">
+      <c r="D165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5793,7 +5823,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6566,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>589</v>
+        <v>268</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>415</v>
+        <v>122</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>284</v>
+        <v>139</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1537</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 159 active clubs (of 173 total).</t>
+          <t>Across 158 active clubs (of 171 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>222</v>
+        <v>103</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -816,26 +816,26 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -872,26 +872,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division G</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -900,23 +900,23 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Division G</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>17</v>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1247,13 +1247,13 @@
         <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1592,1687 +1592,1687 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>8</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E30" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="H30" s="8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="H47" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="8" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="8" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F64" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H64" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F68" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -3281,178 +3281,178 @@
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="E85" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -3461,400 +3461,400 @@
         </is>
       </c>
       <c r="D88" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G88" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H88" s="8" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="G89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" s="6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G92" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H92" s="8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>0</v>
@@ -3863,115 +3863,115 @@
         <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>0</v>
@@ -3983,358 +3983,358 @@
         <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Informatics Institute of Technology</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E114" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>0</v>
@@ -4343,28 +4343,28 @@
         <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
@@ -4373,132 +4373,132 @@
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
@@ -4514,67 +4514,67 @@
         <v>0</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>0</v>
@@ -4583,16 +4583,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E126" s="8" t="n">
         <v>0</v>
@@ -4613,58 +4613,58 @@
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="8" t="n">
         <v>0</v>
@@ -4673,25 +4673,25 @@
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E129" s="6" t="n">
         <v>0</v>
@@ -4703,37 +4703,37 @@
         <v>0</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -4742,46 +4742,46 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E132" s="8" t="n">
         <v>0</v>
@@ -4793,51 +4793,51 @@
         <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>IIT Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
@@ -4847,57 +4847,57 @@
         <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>CSI Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4907,31 +4907,31 @@
         <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" s="6" t="n">
         <v>0</v>
@@ -4940,31 +4940,31 @@
         <v>0</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Codegen Toastmasters</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -4973,21 +4973,21 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
@@ -4997,64 +4997,64 @@
         <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Digana Toastmasters</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>0</v>
@@ -5063,28 +5063,28 @@
         <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Fortude Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
         <v>0</v>
@@ -5093,25 +5093,25 @@
         <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5123,28 +5123,28 @@
         <v>0</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
         <v>0</v>
@@ -5153,21 +5153,21 @@
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5180,24 +5180,24 @@
         <v>0</v>
       </c>
       <c r="G145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Hemas Holdings Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
@@ -5210,28 +5210,28 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" s="6" t="n">
         <v>0</v>
@@ -5243,21 +5243,21 @@
         <v>0</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5278,16 +5278,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5308,16 +5308,16 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,16 +5368,16 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,11 +5398,11 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Esoft Uni Kandy Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Puttalam Toastmasters</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>TalkCrafters Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,16 +5668,16 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5698,16 +5698,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5728,16 +5728,16 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Serendib 7 Star Toastmasters Club</t>
+          <t>iTelaSoft Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5753,36 +5753,6 @@
         <v>0</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>Union Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>E-04</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5823,7 +5793,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5859,52 +5829,52 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>KDU Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>5</v>
@@ -5913,43 +5883,43 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -5958,7 +5928,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>5</v>
@@ -5967,16 +5937,16 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -5985,16 +5955,16 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>3</v>
@@ -6003,34 +5973,34 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>KDU Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>3</v>
@@ -6039,16 +6009,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>3</v>
@@ -6057,127 +6027,127 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>7</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -6566,7 +6536,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6602,16 +6572,16 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -6620,16 +6590,16 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -6638,16 +6608,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -6656,16 +6626,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -6674,16 +6644,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -6692,16 +6662,16 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
@@ -6710,34 +6680,34 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6746,16 +6716,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6764,16 +6734,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6782,16 +6752,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6800,16 +6770,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6818,12 +6788,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -6836,16 +6806,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -6854,16 +6824,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -6872,16 +6842,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -6890,16 +6860,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -6908,16 +6878,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -6926,16 +6896,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -6944,16 +6914,16 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
@@ -6962,16 +6932,16 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>2</v>
@@ -6980,12 +6950,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -6998,12 +6968,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -7016,16 +6986,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -7034,12 +7004,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -7052,16 +7022,16 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
@@ -7070,12 +7040,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -7088,16 +7058,16 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>2</v>
@@ -7106,16 +7076,16 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>2</v>
@@ -7124,16 +7094,16 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>2</v>
@@ -7142,16 +7112,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>2</v>
@@ -7160,16 +7130,16 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>2</v>
@@ -7178,12 +7148,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -7196,12 +7166,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7214,12 +7184,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -7232,12 +7202,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7250,16 +7220,16 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
@@ -7268,16 +7238,16 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>2</v>
@@ -7286,16 +7256,16 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>2</v>
@@ -7304,16 +7274,16 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>2</v>
@@ -7322,12 +7292,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
@@ -7340,55 +7310,55 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5767,10 +5767,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5793,7 +5793,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5880,620 +5880,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>APIIT Kandy Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Awakening Toastmasters</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>C-01</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Braybrooke Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Ceylinco Life Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>HNB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Horana Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Kandy Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>NHCO Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>PIM Toastmasters</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Panadura Toastmasters</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Rajagiriya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Startup Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Smedley Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>CIPM Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Capital Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Central Link Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Dowels Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>HSBC Global Service Centre</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>ICASL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Ja-Ela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Kadawatha Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Kelaniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Matale Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Moratuwa Toastmasters</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>The Millennium Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -6510,10 +5898,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6536,7 +5924,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6572,16 +5960,16 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -6590,16 +5978,16 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -6608,16 +5996,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -6626,16 +6014,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -6644,16 +6032,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -6662,12 +6050,12 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -6680,34 +6068,34 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6716,16 +6104,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6734,16 +6122,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6752,16 +6140,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6770,16 +6158,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6788,653 +6176,41 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Commercial Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Dehiwala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Dialog Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Expolanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>I-01</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>GTN Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>IESL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>IFS Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Kaduwela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Kegalle Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Marketers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Matara Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>NTG Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Nations Toastmasters</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Oasis Toastmasters</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Peradeniya University Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Sampath Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Siyane Toastmasters</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>The Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Tiqri Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Torrington Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>UOC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Voice Your Dream Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday 7 Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>B-03</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>CBL Foods Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CBA Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Central Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Readers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>637</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 158 active clubs (of 171 total).</t>
+          <t>Across 157 active clubs (of 171 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>18</v>
@@ -704,26 +704,26 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Division F</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>16</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>13</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division F</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>16</v>
@@ -816,26 +816,26 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division G</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>18</v>
@@ -872,26 +872,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division G</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -900,26 +900,26 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -1157,13 +1157,13 @@
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>9</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1232,19 +1232,19 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>2</v>
@@ -1253,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>8</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1352,16 +1352,16 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>1</v>
@@ -1370,10 +1370,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1442,16 +1442,16 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>1</v>
@@ -1460,10 +1460,10 @@
         <v>2</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1712,16 +1712,16 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>2</v>
@@ -1730,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1751,160 +1751,160 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>1</v>
@@ -1913,55 +1913,55 @@
         <v>3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>1</v>
@@ -1970,54 +1970,54 @@
         <v>1</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
@@ -2027,22 +2027,22 @@
         <v>2</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2051,123 +2051,123 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
@@ -2177,271 +2177,271 @@
         <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="8" t="n">
         <v>1</v>
@@ -2450,61 +2450,61 @@
         <v>0</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>1</v>
@@ -2513,291 +2513,291 @@
         <v>0</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
@@ -2807,87 +2807,87 @@
         <v>0</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
@@ -2900,121 +2900,121 @@
         <v>1</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>0</v>
@@ -3023,28 +3023,28 @@
         <v>1</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>0</v>
@@ -3053,16 +3053,16 @@
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
@@ -3083,58 +3083,58 @@
         <v>1</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>0</v>
@@ -3143,58 +3143,58 @@
         <v>1</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
@@ -3203,28 +3203,28 @@
         <v>0</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="8" t="n">
         <v>0</v>
@@ -3233,25 +3233,25 @@
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>0</v>
@@ -3260,58 +3260,58 @@
         <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Informatics Institute of Technology</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>1</v>
@@ -3323,28 +3323,28 @@
         <v>0</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>0</v>
@@ -3353,21 +3353,21 @@
         <v>0</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
@@ -3380,19 +3380,19 @@
         <v>0</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -3404,37 +3404,37 @@
         <v>0</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>0</v>
@@ -3443,58 +3443,58 @@
         <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>0</v>
@@ -3503,51 +3503,51 @@
         <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
@@ -3557,31 +3557,31 @@
         <v>0</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" s="8" t="n">
         <v>1</v>
@@ -3590,84 +3590,84 @@
         <v>0</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
@@ -3680,24 +3680,24 @@
         <v>0</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
@@ -3710,88 +3710,88 @@
         <v>0</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>0</v>
@@ -3800,15 +3800,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
@@ -3827,57 +3827,57 @@
         <v>1</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
@@ -3887,18 +3887,18 @@
         <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
@@ -3917,31 +3917,31 @@
         <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>0</v>
@@ -3953,51 +3953,51 @@
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
@@ -4007,57 +4007,57 @@
         <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Informatics Institute of Technology</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
@@ -4070,28 +4070,28 @@
         <v>0</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>0</v>
@@ -4100,61 +4100,61 @@
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>0</v>
@@ -4168,26 +4168,26 @@
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>0</v>
@@ -4198,16 +4198,16 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4228,23 +4228,23 @@
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>0</v>
@@ -4253,21 +4253,21 @@
         <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
@@ -4280,24 +4280,24 @@
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
@@ -4310,24 +4310,24 @@
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
@@ -4340,24 +4340,24 @@
         <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
@@ -4370,24 +4370,24 @@
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
@@ -4397,27 +4397,27 @@
         <v>0</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
@@ -4427,31 +4427,31 @@
         <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="6" t="n">
         <v>0</v>
@@ -4463,21 +4463,21 @@
         <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
@@ -4490,31 +4490,31 @@
         <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
@@ -4523,25 +4523,25 @@
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>CSI Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>0</v>
@@ -4553,25 +4553,25 @@
         <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" s="6" t="n">
         <v>0</v>
@@ -4583,25 +4583,25 @@
         <v>0</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" s="8" t="n">
         <v>0</v>
@@ -4613,25 +4613,25 @@
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Codegen Toastmasters</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>0</v>
@@ -4643,21 +4643,21 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
@@ -4670,24 +4670,24 @@
         <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Digana Toastmasters</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -4708,16 +4708,16 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
@@ -4738,16 +4738,16 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Fortude Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
@@ -4768,11 +4768,11 @@
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
@@ -4798,16 +4798,16 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
@@ -4828,16 +4828,16 @@
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
@@ -4858,16 +4858,16 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CSI Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
@@ -4888,16 +4888,16 @@
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Hemas Holdings Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4918,16 +4918,16 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
@@ -4948,16 +4948,16 @@
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Codegen Toastmasters</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
@@ -4978,16 +4978,16 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
@@ -5008,16 +5008,16 @@
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Digana Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
@@ -5038,16 +5038,16 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5068,16 +5068,16 @@
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Fortude Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
@@ -5098,16 +5098,16 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
@@ -5128,16 +5128,16 @@
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5158,16 +5158,16 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5188,16 +5188,16 @@
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Hemas Holdings Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
@@ -5218,16 +5218,16 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,16 +5248,16 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5278,16 +5278,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5308,16 +5308,16 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,16 +5368,16 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Puttalam Toastmasters</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>TalkCrafters Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>TalkCrafters Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,16 +5668,16 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Union Bank Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5698,16 +5698,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>iTelaSoft Toastmasters Club</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5723,36 +5723,6 @@
         <v>0</v>
       </c>
       <c r="H163" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="n">
-        <v>114</v>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
-        <is>
-          <t>iTelaSoft Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="D164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5767,10 +5737,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5793,7 +5763,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5829,59 +5799,41 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>KDU Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>KDU Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Silvermill Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -5898,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5924,7 +5876,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5912,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -5978,12 +5930,12 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -5996,16 +5948,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -6014,12 +5966,12 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -6032,16 +5984,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -6050,16 +6002,16 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
@@ -6068,149 +6020,23 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>PLC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Panadura Toastmasters</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Smedley Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Vavuniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>hSenid Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>170</v>
+        <v>545</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>80</v>
+        <v>394</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>88</v>
+        <v>268</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>413</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 157 active clubs (of 171 total).</t>
+          <t>Across 155 active clubs (of 172 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -704,26 +704,26 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division F</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division F</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -816,26 +816,26 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division G</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>18</v>
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -900,26 +900,26 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division G</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="F7" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -1352,19 +1352,19 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>2</v>
@@ -1373,7 +1373,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1442,328 +1442,328 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>17</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Kaduwela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>2</v>
@@ -1853,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1952,28 +1952,28 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -2102,28 +2102,28 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -2132,28 +2132,28 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -2162,28 +2162,28 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -2222,28 +2222,28 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -2282,67 +2282,67 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -2351,328 +2351,328 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -2681,49 +2681,49 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -2732,28 +2732,28 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -2762,97 +2762,97 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -2861,169 +2861,169 @@
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -3032,28 +3032,28 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -3062,33 +3062,33 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
@@ -3101,400 +3101,400 @@
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Informatics Institute of Technology</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>0</v>
@@ -3503,295 +3503,295 @@
         <v>0</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E99" s="6" t="n">
         <v>0</v>
@@ -3803,46 +3803,46 @@
         <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3851,217 +3851,217 @@
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>1</v>
@@ -4073,238 +4073,238 @@
         <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
@@ -4313,16 +4313,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>0</v>
@@ -4343,21 +4343,21 @@
         <v>0</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
@@ -4367,91 +4367,91 @@
         <v>0</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E121" s="6" t="n">
         <v>0</v>
@@ -4463,88 +4463,88 @@
         <v>0</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>CSI Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>0</v>
@@ -4553,55 +4553,55 @@
         <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E126" s="8" t="n">
         <v>0</v>
@@ -4613,25 +4613,25 @@
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Codegen Toastmasters</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E127" s="6" t="n">
         <v>0</v>
@@ -4643,51 +4643,51 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>Informatics Institute of Technology</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Digana Toastmasters</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -4697,31 +4697,31 @@
         <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="8" t="n">
         <v>0</v>
@@ -4730,28 +4730,28 @@
         <v>0</v>
       </c>
       <c r="G130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Fortude Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>0</v>
@@ -4760,31 +4760,31 @@
         <v>0</v>
       </c>
       <c r="G131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>0</v>
@@ -4793,21 +4793,21 @@
         <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
@@ -4817,48 +4817,48 @@
         <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
@@ -4883,21 +4883,21 @@
         <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Hemas Holdings Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4907,34 +4907,34 @@
         <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>0</v>
@@ -4943,25 +4943,25 @@
         <v>0</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>0</v>
@@ -4973,28 +4973,28 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0</v>
@@ -5003,28 +5003,28 @@
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
@@ -5033,21 +5033,21 @@
         <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5060,28 +5060,28 @@
         <v>0</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="8" t="n">
         <v>0</v>
@@ -5093,21 +5093,21 @@
         <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
@@ -5120,28 +5120,28 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" s="8" t="n">
         <v>0</v>
@@ -5153,25 +5153,25 @@
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="6" t="n">
         <v>0</v>
@@ -5183,25 +5183,25 @@
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="8" t="n">
         <v>0</v>
@@ -5213,21 +5213,21 @@
         <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,16 +5248,16 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5278,16 +5278,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5308,16 +5308,16 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,16 +5368,16 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,11 +5488,11 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>TalkCrafters Toastmasters Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Union Bank Toastmasters Club</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5663,66 +5663,6 @@
         <v>0</v>
       </c>
       <c r="H161" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>Wednesday 7 Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
-        <is>
-          <t>B-03</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>iTelaSoft Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5737,10 +5677,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5763,7 +5703,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5808,10 +5748,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5832,8 +5772,350 @@
         <v>5</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Dynamic Avenue Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>APIIT Kandy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Awakening Toastmasters</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Baurs Toastmasters Club (BTC)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Ceylinco Life Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>HNB Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Horana Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Kandy Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>NHCO Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>PIM Toastmasters</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Panadura Toastmasters</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Rajagiriya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Ralph Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Sri Lanka Customs Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Startup Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Virtusa Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -5850,10 +6132,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -5876,7 +6158,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5921,7 +6203,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -5939,7 +6221,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -5957,7 +6239,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -5966,16 +6248,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -5984,16 +6266,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -6002,41 +6284,959 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Kandy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>AATSL Emerging Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>AATSL Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Aitken Spence Toastmasters</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Anuradhapura Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>BOI Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Bcis Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Braybrooke Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>CIPM Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>CSE Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Central Link Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Commercial Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Dehiwala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Dialog Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Dowels Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Expolanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>GTN Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>HILL CAPITAL TOASTMASTERS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>HSBC Global Service Centre</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>ICASL Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>IESL Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>IFS Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Kadawatha Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Kaduwela Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Kegalle Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Kelaniya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Marketers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Matale Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Matara Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Minuwangoda Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Moratuwa Toastmasters</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>NTG Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Nations Toastmasters</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Oasis Toastmasters</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Omega Line</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Peradeniya University Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Ragama Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Sampath Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Siyane Toastmasters</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SriLankan Airlines Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Synopsys Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>The Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>The Millennium Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Tiqri Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Torrington Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>UOC Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Voice Your Dream Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday 7 Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>545</v>
+        <v>391</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>394</v>
+        <v>236</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>268</v>
+        <v>191</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1443</v>
+        <v>972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 155 active clubs (of 172 total).</t>
+          <t>Across 162 active clubs (of 171 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -844,26 +844,26 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Division B</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -872,26 +872,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division B</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
         <v>41</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>17</v>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
@@ -1130,10 +1130,10 @@
         <v>5</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -1172,28 +1172,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="F12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="H12" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -1337,13 +1337,13 @@
         <v>6</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1442,427 +1442,427 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="H21" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>The Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>15</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Dowels Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>5</v>
-      </c>
       <c r="H27" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>5</v>
-      </c>
       <c r="H29" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="H33" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1871,70 +1871,70 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>2</v>
@@ -1943,268 +1943,268 @@
         <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>2</v>
@@ -2213,76 +2213,76 @@
         <v>3</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2291,123 +2291,123 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
@@ -2417,154 +2417,154 @@
         <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>2</v>
@@ -2573,67 +2573,67 @@
         <v>3</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>2</v>
@@ -2663,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -2672,139 +2672,139 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>2</v>
@@ -2813,208 +2813,208 @@
         <v>2</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>ICASL Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>2</v>
@@ -3023,895 +3023,895 @@
         <v>2</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F78" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="E79" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="E93" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E95" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E103" s="6" t="n">
         <v>1</v>
@@ -3920,151 +3920,151 @@
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="8" t="n">
         <v>0</v>
@@ -4073,21 +4073,21 @@
         <v>0</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
@@ -4100,75 +4100,75 @@
         <v>0</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="8" t="n">
         <v>0</v>
@@ -4193,51 +4193,51 @@
         <v>0</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Hemas Holdings Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
@@ -4247,91 +4247,91 @@
         <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="n">
         <v>0</v>
@@ -4340,54 +4340,54 @@
         <v>0</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
@@ -4397,61 +4397,61 @@
         <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
         <v>0</v>
@@ -4460,28 +4460,28 @@
         <v>0</v>
       </c>
       <c r="G121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" s="8" t="n">
         <v>1</v>
@@ -4493,58 +4493,58 @@
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>Informatics Institute of Technology</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E124" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="8" t="n">
         <v>0</v>
@@ -4553,55 +4553,55 @@
         <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126" s="8" t="n">
         <v>0</v>
@@ -4613,28 +4613,28 @@
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
@@ -4643,51 +4643,51 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Informatics Institute of Technology</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
@@ -4697,31 +4697,31 @@
         <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" s="8" t="n">
         <v>0</v>
@@ -4733,25 +4733,25 @@
         <v>1</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="6" t="n">
         <v>0</v>
@@ -4763,28 +4763,28 @@
         <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>0</v>
@@ -4793,21 +4793,21 @@
         <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
@@ -4817,64 +4817,64 @@
         <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
@@ -4883,21 +4883,21 @@
         <v>0</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
@@ -4907,27 +4907,27 @@
         <v>0</v>
       </c>
       <c r="F136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
@@ -4948,20 +4948,20 @@
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>0</v>
@@ -4973,28 +4973,28 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0</v>
@@ -5003,28 +5003,28 @@
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
@@ -5033,21 +5033,21 @@
         <v>0</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
@@ -5060,10 +5060,10 @@
         <v>0</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -5072,16 +5072,16 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
         <v>0</v>
@@ -5093,21 +5093,21 @@
         <v>0</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
@@ -5120,28 +5120,28 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="8" t="n">
         <v>0</v>
@@ -5153,25 +5153,25 @@
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>CSI Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="6" t="n">
         <v>0</v>
@@ -5183,25 +5183,25 @@
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" s="8" t="n">
         <v>0</v>
@@ -5213,21 +5213,21 @@
         <v>0</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -5248,16 +5248,16 @@
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Codegen Toastmasters</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
@@ -5278,16 +5278,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>Digana Toastmasters</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5308,16 +5308,16 @@
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5338,16 +5338,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>Fortude Toastmasters Club</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
@@ -5368,16 +5368,16 @@
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Medihelp TMC</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,11 +5548,11 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Rajarata University Toastmasters Club</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,31 +5638,241 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
+          <t>Puttalam Toastmasters</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Rizing Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>SLT Toastmasters</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Sampath Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>TalkCrafters Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
           <t>Union Bank Toastmasters Club</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
+      <c r="C166" s="8" t="inlineStr">
         <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="D161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" s="6" t="n">
+      <c r="D166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Versatile Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>iTelaSoft Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5677,7 +5887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -5703,7 +5913,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5748,10 +5958,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -5793,16 +6003,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
@@ -5811,16 +6021,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4</v>
@@ -5829,16 +6039,16 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -5847,16 +6057,16 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -5865,257 +6075,23 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Horana Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>E-02</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Kandy Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>F-02</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>NHCO Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>PIM Toastmasters</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Panadura Toastmasters</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>I-02</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Rajagiriya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>C-04</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Startup Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>F-04</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -6132,10 +6108,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6158,7 +6134,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6179,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -6248,16 +6224,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -6266,16 +6242,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -6284,48 +6260,48 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -6338,7 +6314,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -6347,7 +6323,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6356,12 +6332,12 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -6374,16 +6350,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6392,16 +6368,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6410,12 +6386,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -6428,16 +6404,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -6446,16 +6422,16 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2</v>
@@ -6464,16 +6440,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>HILL CAPITAL TOASTMASTERS</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -6482,16 +6458,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -6500,16 +6476,16 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>2</v>
@@ -6518,16 +6494,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -6536,34 +6512,34 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>2</v>
@@ -6572,16 +6548,16 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>2</v>
@@ -6590,12 +6566,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -6608,16 +6584,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -6626,16 +6602,16 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>2</v>
@@ -6644,7 +6620,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -6653,7 +6629,7 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
@@ -6662,16 +6638,16 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>2</v>
@@ -6680,563 +6656,23 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>IFS Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>E-03</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Kadawatha Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Kaduwela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>G-01</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Kegalle Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Kelaniya Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Lions Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Marketers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Matale Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Matara Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>A-02</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Moratuwa Toastmasters</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>NTG Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>B-01</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Nations Toastmasters</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>A-03</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Oasis Toastmasters</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Peradeniya University Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>I-04</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>I-03</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Sampath Bank Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Siyane Toastmasters</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>B-04</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>The Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>A-01</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>The Millennium Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>E-01</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Tiqri Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>B-02</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Torrington Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>UOC Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Voice Your Dream Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>F-03</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday 7 Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>B-03</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>391</v>
+        <v>616</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>236</v>
+        <v>454</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>154</v>
+        <v>295</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>191</v>
+        <v>309</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>972</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Across 162 active clubs (of 171 total).</t>
+          <t>Across 164 active clubs (of 174 total).</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>18</v>
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -732,26 +732,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Division C</t>
+          <t>Division A</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -760,26 +760,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Division A</t>
+          <t>Division I</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -788,26 +788,26 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Division I</t>
+          <t>Division H</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -816,23 +816,23 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Division H</t>
+          <t>Division C</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>18</v>
@@ -844,26 +844,26 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Division E</t>
+          <t>Division B</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="D13" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>15</v>
-      </c>
       <c r="F13" s="6" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -872,26 +872,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Division B</t>
+          <t>Division E</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F14" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>17</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>19</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="H7" s="6" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1052,28 +1052,28 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>Panadura Toastmasters</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Avenue Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1160,10 +1160,10 @@
         <v>5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>Baurs Toastmasters Club (BTC)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1187,13 +1187,13 @@
         <v>5</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Kegalle Toastmasters Club</t>
+          <t>Smedley Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1232,28 +1232,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Martin Bauer Hayleys Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1262,28 +1262,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Dialog Toastmasters Club</t>
+          <t>NHCO Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>PLC Toastmasters Club</t>
+          <t>The Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1322,28 +1322,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Dowels Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1352,28 +1352,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Matale Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>Martin Bauer Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Dowels Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Dynamic Avenue Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>The Colombo Toastmasters Club</t>
+          <t>Rajagiriya Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1502,16 +1502,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>5</v>
@@ -1520,10 +1520,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Kelaniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>NHCO Toastmasters Club</t>
+          <t>Kadawatha Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Dehiwala Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>CIPM Toastmasters Club</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>4</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>Kegalle Toastmasters Club</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1682,28 +1682,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Central Link Toastmasters Club</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Ceylinco Life Toastmasters Club</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -1772,28 +1772,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Kadawatha Toastmasters Club</t>
+          <t>PLC Toastmasters Club</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1862,28 +1862,28 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Kelaniya Toastmasters Club</t>
+          <t>The Millennium Toastmasters Club</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>CA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Awakening Toastmasters</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1952,19 +1952,19 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Lyceum Toastmasters Club Nugegoda</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>2</v>
@@ -1973,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Customs Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>PIM Toastmasters</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Virtusa Colombo Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Kaduwela Toastmasters Club</t>
+          <t>HNB Toastmasters Club</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -2102,28 +2102,28 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Ceylinco Life Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -2132,28 +2132,28 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>APIIT Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -2162,28 +2162,28 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -2222,28 +2222,28 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Awakening Toastmasters</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2282,28 +2282,28 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Horana Toastmasters Club</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -2312,28 +2312,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Lions Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2342,16 +2342,16 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Horana Toastmasters Club</t>
+          <t>Lyceum Toastmasters Club Nugegoda</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>4</v>
@@ -2360,10 +2360,10 @@
         <v>2</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2372,28 +2372,28 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>APIIT Kandy Toastmasters Club</t>
+          <t>Virtusa Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2402,28 +2402,28 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>IFS Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2432,28 +2432,28 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>CIPM Toastmasters Club</t>
+          <t>Kandy Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -2462,28 +2462,28 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Lions Toastmasters Club</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -2492,28 +2492,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>UOC Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Sri Lanka Customs Toastmasters Club</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -2552,88 +2552,88 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Oasis Toastmasters</t>
+          <t>Braybrooke Toastmasters Club</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Central Colombo Toastmasters Club</t>
+          <t>Capital Toastmasters Club</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Battaramulla Toastmasters Club</t>
+          <t>Synopsys Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Kandy Lions Toastmasters Club</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>2</v>
@@ -2663,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -2672,28 +2672,28 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Voice Your Dream Toastmasters Club</t>
+          <t>UOC Toastmasters Club</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Anuradhapura Toastmasters Club</t>
+          <t>Oasis Toastmasters</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -2732,28 +2732,28 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>AATSL Toastmasters Club</t>
+          <t>Readers Toastmasters Club</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G66" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -2822,28 +2822,28 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Expolanka Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -2852,28 +2852,28 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Central Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
@@ -2912,109 +2912,109 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ICASL Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>HNB Toastmasters Club</t>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>I-03</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Eswaran Brothers Toastmasters Club</t>
+          <t>Zone24x7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Nations Toastmasters</t>
+          <t>CBA Toastmasters Club</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>2</v>
@@ -3023,658 +3023,658 @@
         <v>2</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Nations Toastmasters</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Galle Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>MillenniumIT ESP Toastmasters</t>
+          <t>NTG Toastmasters Club</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Word Blasters Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G78" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Innovative Minds Toastmasters</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Sampath Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>LOLC Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Commercial Bank Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Maharagama Toastmasters</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>BOI Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Voice Your Dream Toastmasters Club</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G86" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Readers Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Siyane Toastmasters</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Saturday Circle Toastmasters Club</t>
+          <t>CBL Foods Toastmasters Club</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Improvers Toastmasters Club</t>
+          <t>Battaramulla Toastmasters Club</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Zone24x7 Toastmasters Club</t>
+          <t>Peradeniya University Toastmasters Club</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Synopsys Lanka Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Capital Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>LNP Toastmasters Club</t>
+          <t>Siyane Toastmasters</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Mobitel Toastmasters Club</t>
+          <t>NDB Toastmasters</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>1</v>
@@ -3683,355 +3683,355 @@
         <v>2</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Peradeniya University Toastmasters Club</t>
+          <t>MillenniumIT ESP Toastmasters</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>NTG Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>APIIT Toastmasters</t>
+          <t>Eswaran Brothers Toastmasters Club</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Bcis Toastmasters Club</t>
+          <t>CEB Toastmasters Club</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Open University Toastmasters</t>
+          <t>Jaffna Toastmasters Club (JTMC)</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Elicit Toastmasters Club</t>
+          <t>Maharagama Toastmasters</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Batticaloa Toastmasters Club</t>
+          <t>CMA SRI LANKA TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Trailblazers Toastmasters Club</t>
+          <t>CEAT Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CEAT Sri Lanka Toastmasters Club</t>
+          <t>LOLC Toastmasters</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Voice of Colombo Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Sri Lanka Law College Toastmasters Club</t>
+          <t>Improvers Toastmasters Club</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E107" s="6" t="n">
         <v>0</v>
@@ -4040,88 +4040,88 @@
         <v>0</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>DIMO Toastmasters Club</t>
+          <t>Saturday Circle Toastmasters Club</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Word Blasters Toastmasters Club</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Pinnacle Advanced Toastmasters Club</t>
+          <t>Voice of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>0</v>
@@ -4133,88 +4133,88 @@
         <v>2</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Galle Toastmasters Club</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Hemas Holdings Toastmasters Club</t>
+          <t>Abans Toastmasters Club</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>0</v>
@@ -4223,58 +4223,58 @@
         <v>0</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Gampaha Professionals' Toastmasters Club</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>LNP Toastmasters Club</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>1</v>
@@ -4283,205 +4283,205 @@
         <v>1</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>CEB Toastmasters Club</t>
+          <t>Innovative Minds Toastmasters</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>People's Bank Toastmasters Club</t>
+          <t>Elicit Toastmasters Club</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>HUTCH Toastmasters Club</t>
+          <t>People's Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>APIIT Toastmasters</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Batticaloa Toastmasters Club</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>F-04</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>CIMA Sri Lanka Toastmasters Club</t>
+          <t>Sri Lanka Law College Toastmasters Club</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E122" s="8" t="n">
         <v>1</v>
@@ -4490,31 +4490,31 @@
         <v>0</v>
       </c>
       <c r="G122" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Informatics Institute of Technology</t>
+          <t>Hayleys Toastmasters Club</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="D123" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>0</v>
@@ -4523,118 +4523,118 @@
         <v>0</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Yarl Paady Toastmasters Club</t>
+          <t>Pinnacle Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>B-01</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G125" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>LALAN Toastmasters Club</t>
+          <t>Yarl Paady Toastmasters Club</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Sabaragamuwa Toastmasters Club</t>
+          <t>LALAN Toastmasters Club</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D127" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E127" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0</v>
@@ -4643,21 +4643,21 @@
         <v>0</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Serendib Toastmasters Club</t>
+          <t>Mobitel Toastmasters Club</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
@@ -4667,94 +4667,94 @@
         <v>1</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>CIMA Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>IIT Toastmasters Club</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="D131" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>0</v>
@@ -4763,28 +4763,28 @@
         <v>1</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>DFCC Toastmasters</t>
+          <t>DIMO Toastmasters Club</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F132" s="8" t="n">
         <v>0</v>
@@ -4793,115 +4793,115 @@
         <v>0</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>Singer Sri Lanka Toastmasters Club</t>
+          <t>Bank of Ceylon Toastmasters Club</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D133" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Hayleys Toastmasters Club</t>
+          <t>Versatile Toastmasters Club</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D134" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CBA Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D135" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Aitken Spence Toastmasters</t>
+          <t>Open University Toastmasters</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>0</v>
@@ -4910,61 +4910,61 @@
         <v>0</v>
       </c>
       <c r="G136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>NDB Toastmasters</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D137" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E137" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>A J Medichem Toastmasters Club</t>
+          <t>Sabaragamuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E138" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="8" t="n">
         <v>0</v>
@@ -4973,111 +4973,111 @@
         <v>0</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Abans Toastmasters Club</t>
+          <t>Trailblazers Toastmasters Club</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="D139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>HUTCH Toastmasters Club</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F140" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Bank of Ceylon Toastmasters Club</t>
+          <t>Serendib Toastmasters Club</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D141" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Bar Association of Sri Lanka Toastmasters Club</t>
+          <t>Singer Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D142" s="8" t="n">
@@ -5087,31 +5087,31 @@
         <v>0</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>CBL Foods Toastmasters Club</t>
+          <t>University of Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="6" t="n">
         <v>0</v>
@@ -5120,24 +5120,24 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>CSE Toastmasters Club</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="D144" s="8" t="n">
@@ -5147,13 +5147,13 @@
         <v>0</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>CSI Toastmasters Club</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -5177,27 +5177,27 @@
         <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Cargills Bank Toastmasters</t>
+          <t>Bar Association of Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D146" s="8" t="n">
@@ -5210,28 +5210,28 @@
         <v>0</v>
       </c>
       <c r="G146" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Fusion Toastmasters Club</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" s="6" t="n">
         <v>0</v>
@@ -5243,25 +5243,25 @@
         <v>0</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Codegen Toastmasters</t>
+          <t>Prime Group Toastmasters</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>I-01</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="8" t="n">
         <v>0</v>
@@ -5273,21 +5273,21 @@
         <v>0</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Digana Toastmasters</t>
+          <t>Find Your Voice Toastmasters Club</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D149" s="6" t="n">
@@ -5300,24 +5300,24 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>DirectFN Toastmasters</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="D150" s="8" t="n">
@@ -5330,28 +5330,28 @@
         <v>0</v>
       </c>
       <c r="G150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>Fortude Toastmasters Club</t>
+          <t>DFCC Toastmasters</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="6" t="n">
         <v>0</v>
@@ -5363,21 +5363,21 @@
         <v>0</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Club</t>
+          <t>A J Medichem Toastmasters Club</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
@@ -5398,16 +5398,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>GTN Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D153" s="6" t="n">
@@ -5428,16 +5428,16 @@
     </row>
     <row r="154">
       <c r="A154" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Gampaha Professionals' Toastmasters Club</t>
+          <t>Cargills Bank Toastmasters</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
@@ -5458,16 +5458,16 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="D155" s="6" t="n">
@@ -5488,16 +5488,16 @@
     </row>
     <row r="156">
       <c r="A156" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>IESL Sabaragamuwa Toastmaster Club</t>
+          <t>DirectFN Toastmasters</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>E-04</t>
         </is>
       </c>
       <c r="D156" s="8" t="n">
@@ -5518,16 +5518,16 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Esoft Uni Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="D157" s="6" t="n">
@@ -5548,16 +5548,16 @@
     </row>
     <row r="158">
       <c r="A158" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Jaffna Toastmasters Club (JTMC)</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
@@ -5578,16 +5578,16 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>PickMe Toastmasters Club</t>
+          <t>IESL Kandurata Chapter Toastmasters Club</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="D159" s="6" t="n">
@@ -5608,16 +5608,16 @@
     </row>
     <row r="160">
       <c r="A160" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Prime Group Toastmasters</t>
+          <t>IESL Sabaragamuwa Toastmaster Club</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="D160" s="8" t="n">
@@ -5638,16 +5638,16 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Puttalam Toastmasters</t>
+          <t>Medihelp TMC</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="D161" s="6" t="n">
@@ -5668,16 +5668,16 @@
     </row>
     <row r="162">
       <c r="A162" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Rizing Lanka Toastmasters Club</t>
+          <t>PickMe Toastmasters Club</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="D162" s="8" t="n">
@@ -5698,16 +5698,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>SLT Toastmasters</t>
+          <t>Puttalam Toastmasters</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D163" s="6" t="n">
@@ -5728,16 +5728,16 @@
     </row>
     <row r="164">
       <c r="A164" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Sampath Bank Toastmasters Club</t>
+          <t>Rajarata University Toastmasters Club</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>C-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
@@ -5758,16 +5758,16 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>TalkCrafters Toastmasters Club</t>
+          <t>Rizing Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="D165" s="6" t="n">
@@ -5788,16 +5788,16 @@
     </row>
     <row r="166">
       <c r="A166" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Union Bank Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>E-04</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="D166" s="8" t="n">
@@ -5818,16 +5818,16 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>Versatile Toastmasters Club</t>
+          <t>Serendib 7 Star Toastmasters Club</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="D167" s="6" t="n">
@@ -5848,16 +5848,16 @@
     </row>
     <row r="168">
       <c r="A168" s="7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>iTelaSoft Toastmasters Club</t>
+          <t>TalkCrafters Toastmasters Club</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="D168" s="8" t="n">
@@ -5873,6 +5873,66 @@
         <v>0</v>
       </c>
       <c r="H168" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Union Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>E-04</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Wennappuwa Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5887,7 +5947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -5913,7 +5973,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5958,10 +6018,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -6030,7 +6090,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>4</v>
@@ -6048,7 +6108,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
@@ -6066,10 +6126,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -6084,14 +6144,536 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>APIIT Kandy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Awakening Toastmasters</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Baurs Toastmasters Club (BTC)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Ceylinco Life Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>HNB Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Horana Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Kandy Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>PIM Toastmasters</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Panadura Toastmasters</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Rajagiriya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Ralph Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Braybrooke Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Smedley Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Synopsys Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>CA Sri Lanka Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>CIPM Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Capital Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Central Link Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Dowels Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>HILL CAPITAL TOASTMASTERS</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>HSBC Global Service Centre</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Ja-Ela Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Kadawatha Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Kelaniya Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Matale Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Moratuwa Toastmasters</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>The Millennium Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Based on completions as of this snapshot date, not the official Dec 31, 2026 award cutoff. For planning purposes only.</t>
         </is>
@@ -6108,10 +6690,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6134,7 +6716,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6761,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -6197,7 +6779,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -6215,7 +6797,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>2</v>
@@ -6224,16 +6806,16 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>Vavuniya Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
@@ -6242,34 +6824,34 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Smedley Toastmasters Club</t>
+          <t>hSenid Toastmasters Club</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vavuniya Toastmasters Club</t>
+          <t>ECU Sri Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>2</v>
@@ -6278,34 +6860,34 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>hSenid Toastmasters Club</t>
+          <t>Kandy Toastmasters Club</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>I-04</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Baurs Toastmasters Club (BTC)</t>
+          <t>AATSL Emerging Toastmasters Club</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>2</v>
@@ -6314,16 +6896,16 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ECU Sri Lanka Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>2</v>
@@ -6332,16 +6914,16 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Kandy Toastmasters Club</t>
+          <t>Matara Toastmasters Club</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I-04</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
@@ -6350,16 +6932,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>PIM Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>B-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2</v>
@@ -6368,16 +6950,16 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Panadura Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>I-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
@@ -6386,16 +6968,16 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>AATSL Emerging Toastmasters Club</t>
+          <t>Tiqri Toastmasters Club</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>2</v>
@@ -6404,16 +6986,16 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Braybrooke Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="8" t="n">
         <v>2</v>
@@ -6422,12 +7004,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Central Link Toastmasters Club</t>
+          <t>Wednesday 7 Toastmasters Club</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>I-03</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -6440,16 +7022,16 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>HILL CAPITAL TOASTMASTERS</t>
+          <t>AATSL Toastmasters Club</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8" t="n">
         <v>2</v>
@@ -6458,16 +7040,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Aitken Spence Toastmasters</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>I-02</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -6476,12 +7058,12 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Matale Toastmasters Club</t>
+          <t>Anuradhapura Toastmasters Club</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -6494,16 +7076,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Matara Toastmasters Club</t>
+          <t>BOI Toastmasters Club</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>A-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
@@ -6512,30 +7094,30 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Bcis Toastmasters Club</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>CSE Toastmasters Club</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -6548,12 +7130,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Commercial Bank Toastmasters Club</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -6566,16 +7148,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Rajagiriya Toastmasters Club</t>
+          <t>Dehiwala Toastmasters Club</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>2</v>
@@ -6584,16 +7166,16 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>The Millennium Toastmasters Club</t>
+          <t>Dialog Toastmasters Club</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>2</v>
@@ -6602,16 +7184,16 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Tiqri Toastmasters Club</t>
+          <t>Expolanka Toastmasters Club</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>B-02</t>
+          <t>I-01</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>2</v>
@@ -6620,12 +7202,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>GTN Toastmasters Club</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>A-02</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -6638,16 +7220,16 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>IFS Toastmasters Club</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>E-03</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>2</v>
@@ -6656,12 +7238,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Wednesday 7 Toastmasters Club</t>
+          <t>Kaduwela Toastmasters Club</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>B-03</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -6671,8 +7253,368 @@
         <v>2</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Kegalle Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Lions Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Marketers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Minuwangoda Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>NTG Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Nations Toastmasters</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Oasis Toastmasters</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Peradeniya University Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>I-04</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Professionals Beyond Boundaries Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Sampath Bank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Siyane Toastmasters</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>SriLankan Airlines Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>The Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>UOC Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Voice Your Dream Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>CBL Foods Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>CBA Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Central Colombo Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Readers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Clubs achieving Excellence tier are shown only in the Excellence table, per award rules.</t>
         </is>

--- a/docs/exports/district/District_82_Summary.xlsx
+++ b/docs/exports/district/District_82_Summary.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
